--- a/backend/outputFile/IntegrationOut.xlsx
+++ b/backend/outputFile/IntegrationOut.xlsx
@@ -23,7 +23,7 @@
     <t>Amount Stored</t>
   </si>
   <si>
-    <t>PS PAC I</t>
+    <t>PS PAC I (56,67000, 13,34000)</t>
   </si>
   <si>
     <t>AMBIENT</t>
